--- a/artfynd/A 46594-2024 artfynd.xlsx
+++ b/artfynd/A 46594-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121237811</v>
+        <v>121238545</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503902</v>
+        <v>503854</v>
       </c>
       <c r="R2" t="n">
-        <v>6985352</v>
+        <v>6985434</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121238207</v>
+        <v>121238193</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>78683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503839</v>
+        <v>503849</v>
       </c>
       <c r="R3" t="n">
-        <v>6985431</v>
+        <v>6985442</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,7 +906,7 @@
         <v>121241245</v>
       </c>
       <c r="B4" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121237988</v>
+        <v>121237811</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,17 +1051,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503961</v>
+        <v>503902</v>
       </c>
       <c r="R5" t="n">
-        <v>6985423</v>
+        <v>6985352</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121238545</v>
+        <v>121238312</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503854</v>
+        <v>503818</v>
       </c>
       <c r="R6" t="n">
-        <v>6985434</v>
+        <v>6985444</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1198,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121238312</v>
+        <v>121238207</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1251,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1279,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503818</v>
+        <v>503839</v>
       </c>
       <c r="R7" t="n">
-        <v>6985444</v>
+        <v>6985431</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238193</v>
+        <v>121237988</v>
       </c>
       <c r="B8" t="n">
-        <v>78680</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,37 +1367,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503849</v>
+        <v>503961</v>
       </c>
       <c r="R8" t="n">
-        <v>6985442</v>
+        <v>6985423</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1425,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,7 +1445,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46594-2024 artfynd.xlsx
+++ b/artfynd/A 46594-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121238545</v>
+        <v>121238312</v>
       </c>
       <c r="B2" t="n">
         <v>78601</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503854</v>
+        <v>503818</v>
       </c>
       <c r="R2" t="n">
-        <v>6985434</v>
+        <v>6985444</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121241245</v>
+        <v>121237811</v>
       </c>
       <c r="B4" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503875</v>
+        <v>503902</v>
       </c>
       <c r="R4" t="n">
-        <v>6985328</v>
+        <v>6985352</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121237811</v>
+        <v>121238545</v>
       </c>
       <c r="B5" t="n">
         <v>78601</v>
@@ -1051,17 +1051,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503902</v>
+        <v>503854</v>
       </c>
       <c r="R5" t="n">
-        <v>6985352</v>
+        <v>6985434</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121238312</v>
+        <v>121237988</v>
       </c>
       <c r="B6" t="n">
         <v>78601</v>
@@ -1163,14 +1163,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503818</v>
+        <v>503961</v>
       </c>
       <c r="R6" t="n">
-        <v>6985444</v>
+        <v>6985423</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121238207</v>
+        <v>121241245</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>90715</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,41 +1251,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503839</v>
+        <v>503875</v>
       </c>
       <c r="R7" t="n">
-        <v>6985431</v>
+        <v>6985328</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121237988</v>
+        <v>121238207</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,41 +1363,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503961</v>
+        <v>503839</v>
       </c>
       <c r="R8" t="n">
-        <v>6985423</v>
+        <v>6985431</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 46594-2024 artfynd.xlsx
+++ b/artfynd/A 46594-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121238312</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>121238193</v>
       </c>
       <c r="B3" t="n">
-        <v>78683</v>
+        <v>78686</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121237811</v>
+        <v>121237988</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,17 +939,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503902</v>
+        <v>503961</v>
       </c>
       <c r="R4" t="n">
-        <v>6985352</v>
+        <v>6985423</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121238545</v>
+        <v>121237811</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,17 +1051,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503854</v>
+        <v>503902</v>
       </c>
       <c r="R5" t="n">
-        <v>6985434</v>
+        <v>6985352</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121237988</v>
+        <v>121238545</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,14 +1163,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503961</v>
+        <v>503854</v>
       </c>
       <c r="R6" t="n">
-        <v>6985423</v>
+        <v>6985434</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,7 +1242,7 @@
         <v>121241245</v>
       </c>
       <c r="B7" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>121238207</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 46594-2024 artfynd.xlsx
+++ b/artfynd/A 46594-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121238312</v>
+        <v>121241245</v>
       </c>
       <c r="B2" t="n">
-        <v>78604</v>
+        <v>90728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503818</v>
+        <v>503875</v>
       </c>
       <c r="R2" t="n">
-        <v>6985444</v>
+        <v>6985328</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121237988</v>
+        <v>121238545</v>
       </c>
       <c r="B4" t="n">
         <v>78604</v>
@@ -939,14 +939,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503961</v>
+        <v>503854</v>
       </c>
       <c r="R4" t="n">
-        <v>6985423</v>
+        <v>6985434</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121237811</v>
+        <v>121238312</v>
       </c>
       <c r="B5" t="n">
         <v>78604</v>
@@ -1051,17 +1051,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503902</v>
+        <v>503818</v>
       </c>
       <c r="R5" t="n">
-        <v>6985352</v>
+        <v>6985444</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121238545</v>
+        <v>121237811</v>
       </c>
       <c r="B6" t="n">
         <v>78604</v>
@@ -1163,17 +1163,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503854</v>
+        <v>503902</v>
       </c>
       <c r="R6" t="n">
-        <v>6985434</v>
+        <v>6985352</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121241245</v>
+        <v>121237988</v>
       </c>
       <c r="B7" t="n">
-        <v>90727</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,34 +1255,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503875</v>
+        <v>503961</v>
       </c>
       <c r="R7" t="n">
-        <v>6985328</v>
+        <v>6985423</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,7 +1354,7 @@
         <v>121238207</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 46594-2024 artfynd.xlsx
+++ b/artfynd/A 46594-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121241245</v>
       </c>
       <c r="B2" t="n">
-        <v>90728</v>
+        <v>90731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121238193</v>
+        <v>121238207</v>
       </c>
       <c r="B3" t="n">
-        <v>78686</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,44 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503849</v>
+        <v>503839</v>
       </c>
       <c r="R3" t="n">
-        <v>6985442</v>
+        <v>6985431</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121238545</v>
+        <v>121238312</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503854</v>
+        <v>503818</v>
       </c>
       <c r="R4" t="n">
-        <v>6985434</v>
+        <v>6985444</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -978,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121238312</v>
+        <v>121238545</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503818</v>
+        <v>503854</v>
       </c>
       <c r="R5" t="n">
-        <v>6985444</v>
+        <v>6985434</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121237811</v>
+        <v>121238193</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>78689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,37 +1139,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503902</v>
+        <v>503849</v>
       </c>
       <c r="R6" t="n">
-        <v>6985352</v>
+        <v>6985442</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,6 +1220,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121237988</v>
+        <v>121237811</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,17 +1275,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503961</v>
+        <v>503902</v>
       </c>
       <c r="R7" t="n">
-        <v>6985423</v>
+        <v>6985352</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238207</v>
+        <v>121237988</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,41 +1363,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503839</v>
+        <v>503961</v>
       </c>
       <c r="R8" t="n">
-        <v>6985431</v>
+        <v>6985423</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 46594-2024 artfynd.xlsx
+++ b/artfynd/A 46594-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121241245</v>
+        <v>121238312</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503875</v>
+        <v>503818</v>
       </c>
       <c r="R2" t="n">
-        <v>6985328</v>
+        <v>6985444</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121238207</v>
+        <v>121238193</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>78689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503839</v>
+        <v>503849</v>
       </c>
       <c r="R3" t="n">
-        <v>6985431</v>
+        <v>6985442</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121238312</v>
+        <v>121238545</v>
       </c>
       <c r="B4" t="n">
         <v>78607</v>
@@ -939,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503818</v>
+        <v>503854</v>
       </c>
       <c r="R4" t="n">
-        <v>6985444</v>
+        <v>6985434</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121238545</v>
+        <v>121241245</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1031,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503854</v>
+        <v>503875</v>
       </c>
       <c r="R5" t="n">
-        <v>6985434</v>
+        <v>6985328</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121238193</v>
+        <v>121238207</v>
       </c>
       <c r="B6" t="n">
-        <v>78689</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,44 +1139,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503849</v>
+        <v>503839</v>
       </c>
       <c r="R6" t="n">
-        <v>6985442</v>
+        <v>6985431</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1221,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46594-2024 artfynd.xlsx
+++ b/artfynd/A 46594-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121238545</v>
+        <v>121241245</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503854</v>
+        <v>503875</v>
       </c>
       <c r="R4" t="n">
-        <v>6985434</v>
+        <v>6985328</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121241245</v>
+        <v>121238545</v>
       </c>
       <c r="B5" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,34 +1031,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503875</v>
+        <v>503854</v>
       </c>
       <c r="R5" t="n">
-        <v>6985328</v>
+        <v>6985434</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 46594-2024 artfynd.xlsx
+++ b/artfynd/A 46594-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121241245</v>
+        <v>121238545</v>
       </c>
       <c r="B4" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503875</v>
+        <v>503854</v>
       </c>
       <c r="R4" t="n">
-        <v>6985328</v>
+        <v>6985434</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121238545</v>
+        <v>121241245</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,34 +1031,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503854</v>
+        <v>503875</v>
       </c>
       <c r="R5" t="n">
-        <v>6985434</v>
+        <v>6985328</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 46594-2024 artfynd.xlsx
+++ b/artfynd/A 46594-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121238312</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121238193</v>
+        <v>121241245</v>
       </c>
       <c r="B3" t="n">
-        <v>78689</v>
+        <v>90737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503849</v>
+        <v>503875</v>
       </c>
       <c r="R3" t="n">
-        <v>6985442</v>
+        <v>6985328</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -865,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -906,7 +902,7 @@
         <v>121238545</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121241245</v>
+        <v>121238193</v>
       </c>
       <c r="B5" t="n">
-        <v>90731</v>
+        <v>78690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,34 +1027,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503875</v>
+        <v>503849</v>
       </c>
       <c r="R5" t="n">
-        <v>6985328</v>
+        <v>6985442</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,6 +1108,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121238207</v>
+        <v>121237811</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,38 +1139,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503839</v>
+        <v>503902</v>
       </c>
       <c r="R6" t="n">
-        <v>6985431</v>
+        <v>6985352</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121237811</v>
+        <v>121237988</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,17 +1275,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503902</v>
+        <v>503961</v>
       </c>
       <c r="R7" t="n">
-        <v>6985352</v>
+        <v>6985423</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121237988</v>
+        <v>121238207</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,41 +1363,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503961</v>
+        <v>503839</v>
       </c>
       <c r="R8" t="n">
-        <v>6985423</v>
+        <v>6985431</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 46594-2024 artfynd.xlsx
+++ b/artfynd/A 46594-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121238312</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121241245</v>
+        <v>121238193</v>
       </c>
       <c r="B3" t="n">
-        <v>90737</v>
+        <v>78691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503875</v>
+        <v>503849</v>
       </c>
       <c r="R3" t="n">
-        <v>6985328</v>
+        <v>6985442</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121238545</v>
+        <v>121241245</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503854</v>
+        <v>503875</v>
       </c>
       <c r="R4" t="n">
-        <v>6985434</v>
+        <v>6985328</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121238193</v>
+        <v>121238545</v>
       </c>
       <c r="B5" t="n">
-        <v>78690</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,37 +1031,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503849</v>
+        <v>503854</v>
       </c>
       <c r="R5" t="n">
-        <v>6985442</v>
+        <v>6985434</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1089,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1109,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121237811</v>
+        <v>121237988</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,17 +1163,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503902</v>
+        <v>503961</v>
       </c>
       <c r="R6" t="n">
-        <v>6985352</v>
+        <v>6985423</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121237988</v>
+        <v>121238207</v>
       </c>
       <c r="B7" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,41 +1251,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503961</v>
+        <v>503839</v>
       </c>
       <c r="R7" t="n">
-        <v>6985423</v>
+        <v>6985431</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238207</v>
+        <v>121237811</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,38 +1363,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503839</v>
+        <v>503902</v>
       </c>
       <c r="R8" t="n">
-        <v>6985431</v>
+        <v>6985352</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 46594-2024 artfynd.xlsx
+++ b/artfynd/A 46594-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121238312</v>
+        <v>121237988</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503818</v>
+        <v>503961</v>
       </c>
       <c r="R2" t="n">
-        <v>6985444</v>
+        <v>6985423</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121238193</v>
+        <v>121237811</v>
       </c>
       <c r="B3" t="n">
-        <v>78691</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,40 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503849</v>
+        <v>503902</v>
       </c>
       <c r="R3" t="n">
-        <v>6985442</v>
+        <v>6985352</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121238545</v>
+        <v>121238193</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>78691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,34 +1027,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503854</v>
+        <v>503849</v>
       </c>
       <c r="R5" t="n">
-        <v>6985434</v>
+        <v>6985442</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,6 +1108,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121237988</v>
+        <v>121238545</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1163,14 +1163,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503961</v>
+        <v>503854</v>
       </c>
       <c r="R6" t="n">
-        <v>6985423</v>
+        <v>6985434</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1351,7 +1351,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121237811</v>
+        <v>121238312</v>
       </c>
       <c r="B8" t="n">
         <v>78609</v>
@@ -1387,17 +1387,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503902</v>
+        <v>503818</v>
       </c>
       <c r="R8" t="n">
-        <v>6985352</v>
+        <v>6985444</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 46594-2024 artfynd.xlsx
+++ b/artfynd/A 46594-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121237988</v>
+        <v>121238207</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503961</v>
+        <v>503839</v>
       </c>
       <c r="R2" t="n">
-        <v>6985423</v>
+        <v>6985431</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121237811</v>
+        <v>121238545</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -823,17 +823,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503902</v>
+        <v>503854</v>
       </c>
       <c r="R3" t="n">
-        <v>6985352</v>
+        <v>6985434</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121241245</v>
+        <v>121237811</v>
       </c>
       <c r="B4" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503875</v>
+        <v>503902</v>
       </c>
       <c r="R4" t="n">
-        <v>6985328</v>
+        <v>6985352</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121238193</v>
+        <v>121241245</v>
       </c>
       <c r="B5" t="n">
-        <v>78691</v>
+        <v>90738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,37 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503849</v>
+        <v>503875</v>
       </c>
       <c r="R5" t="n">
-        <v>6985442</v>
+        <v>6985328</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1089,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1105,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121238545</v>
+        <v>121237988</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1163,14 +1159,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503854</v>
+        <v>503961</v>
       </c>
       <c r="R6" t="n">
-        <v>6985434</v>
+        <v>6985423</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1202,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121238207</v>
+        <v>121238312</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503839</v>
+        <v>503818</v>
       </c>
       <c r="R7" t="n">
-        <v>6985431</v>
+        <v>6985444</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238312</v>
+        <v>121238193</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>78691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,34 +1363,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503818</v>
+        <v>503849</v>
       </c>
       <c r="R8" t="n">
-        <v>6985444</v>
+        <v>6985442</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1426,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1435,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,6 +1444,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46594-2024 artfynd.xlsx
+++ b/artfynd/A 46594-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121238207</v>
+        <v>121238545</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503839</v>
+        <v>503854</v>
       </c>
       <c r="R2" t="n">
-        <v>6985431</v>
+        <v>6985434</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121238545</v>
+        <v>121238312</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503854</v>
+        <v>503818</v>
       </c>
       <c r="R3" t="n">
-        <v>6985434</v>
+        <v>6985444</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121237811</v>
+        <v>121238207</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503902</v>
+        <v>503839</v>
       </c>
       <c r="R4" t="n">
-        <v>6985352</v>
+        <v>6985431</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121241245</v>
+        <v>121237988</v>
       </c>
       <c r="B5" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Säckenänget, Säckenänget, Jmt</t>
+          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503875</v>
+        <v>503961</v>
       </c>
       <c r="R5" t="n">
-        <v>6985328</v>
+        <v>6985423</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121237988</v>
+        <v>121238193</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>78691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1139,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gårdstjärnbäcken, Gårdstjärnbäcken, Jmt</t>
+          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503961</v>
+        <v>503849</v>
       </c>
       <c r="R6" t="n">
-        <v>6985423</v>
+        <v>6985442</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1198,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,6 +1220,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1235,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121238312</v>
+        <v>121241245</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1255,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503818</v>
+        <v>503875</v>
       </c>
       <c r="R7" t="n">
-        <v>6985444</v>
+        <v>6985328</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1310,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238193</v>
+        <v>121237811</v>
       </c>
       <c r="B8" t="n">
-        <v>78691</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,40 +1367,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nils-Erikbodarna, Nils-Erikbodarna, Jmt</t>
+          <t>Säckenänget, Säckenänget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503849</v>
+        <v>503902</v>
       </c>
       <c r="R8" t="n">
-        <v>6985442</v>
+        <v>6985352</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,7 +1445,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
